--- a/data/sars/keys/area_key_atlantic_final.xlsx
+++ b/data/sars/keys/area_key_atlantic_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Library/CloudStorage/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/keys/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6421B73A-AEBC-804A-8B76-2BFFA3990FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997C1EB5-7B97-754F-98B5-2AC7CA96C550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="1200" windowWidth="28040" windowHeight="17440" xr2:uid="{9139CB3F-BC9E-A548-9F2C-BB82AE123E2F}"/>
+    <workbookView xWindow="1360" yWindow="1200" windowWidth="28040" windowHeight="17440" xr2:uid="{9139CB3F-BC9E-A548-9F2C-BB82AE123E2F}"/>
   </bookViews>
   <sheets>
     <sheet name="area_key_atlantic_final" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="249">
   <si>
     <t>comm_name</t>
   </si>
@@ -169,9 +169,6 @@
     <t>Eastern Gulf of Mexico</t>
   </si>
   <si>
-    <t>Eastern Gulf of Mexico Coastal</t>
-  </si>
-  <si>
     <t>Eastern Gulf of Mexico coastal</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>Gulf of America, Continental Shelf</t>
   </si>
   <si>
-    <t>Northern Gulf of Mexico Continental Shelf</t>
-  </si>
-  <si>
     <t>Gulf of America, Eastern Coastal</t>
   </si>
   <si>
@@ -373,9 +367,6 @@
     <t>Northern Gulf of Mexico Coastal</t>
   </si>
   <si>
-    <t>Northern Gulf of Mexico Coastal Stocks</t>
-  </si>
-  <si>
     <t>Northern Gulf of Mexico Coastal (3 stocks)</t>
   </si>
   <si>
@@ -527,9 +518,6 @@
   </si>
   <si>
     <t>Western Gulf of Mexico</t>
-  </si>
-  <si>
-    <t>Western Gulf of Mexico Coastal</t>
   </si>
   <si>
     <t>Western Gulf of Mexico coastal</t>
@@ -1669,7 +1657,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1823,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -1837,7 +1825,7 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1935,7 +1923,7 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1949,7 +1937,7 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -2117,7 +2105,7 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -2187,7 +2175,7 @@
         <v>27</v>
       </c>
       <c r="D38" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -2271,7 +2259,7 @@
         <v>34</v>
       </c>
       <c r="D44" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -2285,7 +2273,7 @@
         <v>35</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -2422,7 +2410,7 @@
         <v>47</v>
       </c>
       <c r="C55" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
         <v>6</v>
@@ -2433,10 +2421,10 @@
         <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
@@ -2447,10 +2435,10 @@
         <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>6</v>
@@ -2461,10 +2449,10 @@
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>6</v>
@@ -2475,10 +2463,10 @@
         <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>6</v>
@@ -2489,10 +2477,10 @@
         <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>6</v>
@@ -2503,10 +2491,10 @@
         <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>6</v>
@@ -2517,10 +2505,10 @@
         <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -2531,10 +2519,10 @@
         <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D63" t="s">
         <v>6</v>
@@ -2545,10 +2533,10 @@
         <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
         <v>6</v>
@@ -2559,10 +2547,10 @@
         <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
         <v>6</v>
@@ -2573,10 +2561,10 @@
         <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C66" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
         <v>6</v>
@@ -2587,10 +2575,10 @@
         <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D67" t="s">
         <v>6</v>
@@ -2601,10 +2589,10 @@
         <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
@@ -2615,10 +2603,10 @@
         <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D69" t="s">
         <v>6</v>
@@ -2629,10 +2617,10 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D70" t="s">
         <v>6</v>
@@ -2643,10 +2631,10 @@
         <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D71" t="s">
         <v>6</v>
@@ -2657,10 +2645,10 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C72" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D72" t="s">
         <v>6</v>
@@ -2671,13 +2659,13 @@
         <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D73" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -2685,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D74" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -2699,13 +2687,13 @@
         <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D75" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -2713,10 +2701,10 @@
         <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>6</v>
@@ -2727,10 +2715,10 @@
         <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>6</v>
@@ -2741,10 +2729,10 @@
         <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C78" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>6</v>
@@ -2755,10 +2743,10 @@
         <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>6</v>
@@ -2769,10 +2757,10 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C80" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>6</v>
@@ -2783,10 +2771,10 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C81" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D81" t="s">
         <v>6</v>
@@ -2797,10 +2785,10 @@
         <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C82" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D82" t="s">
         <v>6</v>
@@ -2811,10 +2799,10 @@
         <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C83" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D83" t="s">
         <v>6</v>
@@ -2825,10 +2813,10 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C84" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D84" t="s">
         <v>6</v>
@@ -2839,10 +2827,10 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D85" t="s">
         <v>6</v>
@@ -2853,10 +2841,10 @@
         <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C86" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D86" t="s">
         <v>6</v>
@@ -2867,10 +2855,10 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>6</v>
@@ -2881,10 +2869,10 @@
         <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C88" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>6</v>
@@ -2895,10 +2883,10 @@
         <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>6</v>
@@ -2909,13 +2897,13 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C90" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D90" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -2923,13 +2911,13 @@
         <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C91" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D91" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -2937,13 +2925,13 @@
         <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D92" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -2954,7 +2942,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D93" t="s">
         <v>6</v>
@@ -2968,7 +2956,7 @@
         <v>5</v>
       </c>
       <c r="C94" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D94" t="s">
         <v>6</v>
@@ -2979,10 +2967,10 @@
         <v>22</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C95" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D95" t="s">
         <v>6</v>
@@ -2993,10 +2981,10 @@
         <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C96" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D96" t="s">
         <v>6</v>
@@ -3007,10 +2995,10 @@
         <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D97" t="s">
         <v>6</v>
@@ -3021,10 +3009,10 @@
         <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C98" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D98" t="s">
         <v>6</v>
@@ -3035,10 +3023,10 @@
         <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C99" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D99" t="s">
         <v>6</v>
@@ -3049,10 +3037,10 @@
         <v>22</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C100" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D100" t="s">
         <v>6</v>
@@ -3063,10 +3051,10 @@
         <v>22</v>
       </c>
       <c r="B101" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D101" t="s">
         <v>6</v>
@@ -3077,10 +3065,10 @@
         <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
@@ -3091,10 +3079,10 @@
         <v>22</v>
       </c>
       <c r="B103" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C103" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="D103" t="s">
         <v>6</v>
@@ -3105,10 +3093,10 @@
         <v>22</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D104" t="s">
         <v>6</v>
@@ -3119,10 +3107,10 @@
         <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C105" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D105" t="s">
         <v>6</v>
@@ -3133,10 +3121,10 @@
         <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D106" t="s">
         <v>6</v>
@@ -3147,10 +3135,10 @@
         <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C107" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D107" t="s">
         <v>6</v>
@@ -3161,10 +3149,10 @@
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C108" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D108" t="s">
         <v>6</v>
@@ -3175,10 +3163,10 @@
         <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>58</v>
+        <v>247</v>
       </c>
       <c r="D109" t="s">
         <v>6</v>
@@ -3189,10 +3177,10 @@
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C110" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
@@ -3203,10 +3191,10 @@
         <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C111" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D111" t="s">
         <v>6</v>
@@ -3217,10 +3205,10 @@
         <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D112" t="s">
         <v>6</v>
@@ -3231,10 +3219,10 @@
         <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D113" t="s">
         <v>6</v>
@@ -3245,10 +3233,10 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C114" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D114" t="s">
         <v>6</v>
@@ -3259,10 +3247,10 @@
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D115" t="s">
         <v>6</v>
@@ -3273,7 +3261,7 @@
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
@@ -3301,7 +3289,7 @@
         <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
@@ -3329,13 +3317,13 @@
         <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D120" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -3343,13 +3331,13 @@
         <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C121" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D121" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -3357,10 +3345,10 @@
         <v>22</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C122" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>6</v>
@@ -3371,10 +3359,10 @@
         <v>22</v>
       </c>
       <c r="B123" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>6</v>
@@ -3385,10 +3373,10 @@
         <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C124" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>6</v>
@@ -3399,10 +3387,10 @@
         <v>22</v>
       </c>
       <c r="B125" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C125" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>6</v>
@@ -3413,10 +3401,10 @@
         <v>22</v>
       </c>
       <c r="B126" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>6</v>
@@ -3427,10 +3415,10 @@
         <v>22</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C127" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>6</v>
@@ -3441,10 +3429,10 @@
         <v>22</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>6</v>
@@ -3497,10 +3485,10 @@
         <v>22</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C132" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>6</v>
@@ -3511,10 +3499,10 @@
         <v>22</v>
       </c>
       <c r="B133" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C133" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>6</v>
@@ -3525,10 +3513,10 @@
         <v>22</v>
       </c>
       <c r="B134" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C134" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>6</v>
@@ -3539,10 +3527,10 @@
         <v>22</v>
       </c>
       <c r="B135" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C135" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>6</v>
@@ -3553,13 +3541,13 @@
         <v>22</v>
       </c>
       <c r="B136" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C136" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D136" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -3567,13 +3555,13 @@
         <v>22</v>
       </c>
       <c r="B137" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C137" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D137" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -3581,10 +3569,10 @@
         <v>22</v>
       </c>
       <c r="B138" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C138" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>6</v>
@@ -3595,10 +3583,10 @@
         <v>22</v>
       </c>
       <c r="B139" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C139" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>6</v>
@@ -3609,10 +3597,10 @@
         <v>22</v>
       </c>
       <c r="B140" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C140" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>6</v>
@@ -3623,10 +3611,10 @@
         <v>22</v>
       </c>
       <c r="B141" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C141" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>6</v>
@@ -3637,10 +3625,10 @@
         <v>22</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C142" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>6</v>
@@ -3651,10 +3639,10 @@
         <v>22</v>
       </c>
       <c r="B143" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C143" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>6</v>
@@ -3665,10 +3653,10 @@
         <v>22</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>6</v>
@@ -3679,10 +3667,10 @@
         <v>22</v>
       </c>
       <c r="B145" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C145" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>6</v>
@@ -3693,10 +3681,10 @@
         <v>22</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C146" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>6</v>
@@ -3707,10 +3695,10 @@
         <v>22</v>
       </c>
       <c r="B147" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C147" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>6</v>
@@ -3721,10 +3709,10 @@
         <v>22</v>
       </c>
       <c r="B148" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>6</v>
@@ -3735,10 +3723,10 @@
         <v>22</v>
       </c>
       <c r="B149" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C149" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>6</v>
@@ -3749,10 +3737,10 @@
         <v>22</v>
       </c>
       <c r="B150" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C150" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>6</v>
@@ -3763,10 +3751,10 @@
         <v>22</v>
       </c>
       <c r="B151" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C151" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>6</v>
@@ -3777,10 +3765,10 @@
         <v>22</v>
       </c>
       <c r="B152" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C152" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>6</v>
@@ -3791,10 +3779,10 @@
         <v>22</v>
       </c>
       <c r="B153" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C153" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>6</v>
@@ -3805,10 +3793,10 @@
         <v>22</v>
       </c>
       <c r="B154" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C154" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>6</v>
@@ -3819,10 +3807,10 @@
         <v>22</v>
       </c>
       <c r="B155" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C155" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>6</v>
@@ -3833,10 +3821,10 @@
         <v>22</v>
       </c>
       <c r="B156" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>6</v>
@@ -3847,10 +3835,10 @@
         <v>22</v>
       </c>
       <c r="B157" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C157" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>6</v>
@@ -3861,10 +3849,10 @@
         <v>22</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C158" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>6</v>
@@ -3875,10 +3863,10 @@
         <v>22</v>
       </c>
       <c r="B159" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C159" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>6</v>
@@ -3889,10 +3877,10 @@
         <v>22</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C160" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="D160" t="s">
         <v>6</v>
@@ -3903,10 +3891,10 @@
         <v>22</v>
       </c>
       <c r="B161" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C161" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="D161" t="s">
         <v>6</v>
@@ -3917,13 +3905,13 @@
         <v>22</v>
       </c>
       <c r="B162" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C162" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D162" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
@@ -3931,10 +3919,10 @@
         <v>22</v>
       </c>
       <c r="B163" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C163" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>6</v>
@@ -3945,10 +3933,10 @@
         <v>22</v>
       </c>
       <c r="B164" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C164" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>6</v>
@@ -3959,13 +3947,13 @@
         <v>22</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C165" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D165" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
@@ -3973,13 +3961,13 @@
         <v>22</v>
       </c>
       <c r="B166" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C166" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D166" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
@@ -3987,27 +3975,27 @@
         <v>22</v>
       </c>
       <c r="B167" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C167" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D167" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="B168" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C168" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D168" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
@@ -4015,13 +4003,13 @@
         <v>22</v>
       </c>
       <c r="B169" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="C169" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D169" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
@@ -4029,13 +4017,13 @@
         <v>22</v>
       </c>
       <c r="B170" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C170" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D170" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
@@ -4043,27 +4031,27 @@
         <v>22</v>
       </c>
       <c r="B171" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C171" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D171" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="B172" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="C172" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D172" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
@@ -4071,13 +4059,13 @@
         <v>22</v>
       </c>
       <c r="B173" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="C173" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D173" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
@@ -4085,13 +4073,13 @@
         <v>22</v>
       </c>
       <c r="B174" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C174" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D174" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
@@ -4099,13 +4087,13 @@
         <v>22</v>
       </c>
       <c r="B175" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C175" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D175" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
@@ -4113,13 +4101,13 @@
         <v>22</v>
       </c>
       <c r="B176" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C176" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D176" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
@@ -4127,13 +4115,13 @@
         <v>22</v>
       </c>
       <c r="B177" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C177" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D177" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
@@ -4141,13 +4129,13 @@
         <v>22</v>
       </c>
       <c r="B178" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="C178" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D178" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
@@ -4155,13 +4143,13 @@
         <v>22</v>
       </c>
       <c r="B179" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C179" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D179" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
@@ -4169,13 +4157,13 @@
         <v>22</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C180" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D180" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
@@ -4183,13 +4171,13 @@
         <v>22</v>
       </c>
       <c r="B181" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C181" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D181" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
@@ -4197,32 +4185,32 @@
         <v>22</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C182" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D182" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>22</v>
+        <v>248</v>
       </c>
       <c r="B183" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C183" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="D183" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B184" t="s">
         <v>14</v>
@@ -4231,12 +4219,12 @@
         <v>14</v>
       </c>
       <c r="D184" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B185" t="s">
         <v>4</v>
@@ -4250,7 +4238,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B186" t="s">
         <v>6</v>
@@ -4264,7 +4252,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B187" t="s">
         <v>17</v>
@@ -4278,7 +4266,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B188" t="s">
         <v>8</v>
@@ -4292,7 +4280,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B189" t="s">
         <v>5</v>
@@ -4306,7 +4294,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B190" t="s">
         <v>18</v>
@@ -4320,7 +4308,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B191" t="s">
         <v>11</v>
@@ -4334,7 +4322,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B192" t="s">
         <v>12</v>
@@ -4348,7 +4336,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B193" t="s">
         <v>13</v>
@@ -4362,7 +4350,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B194" t="s">
         <v>14</v>
@@ -4371,12 +4359,12 @@
         <v>14</v>
       </c>
       <c r="D194" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B195" t="s">
         <v>4</v>
@@ -4390,7 +4378,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B196" t="s">
         <v>6</v>
@@ -4404,7 +4392,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B197" t="s">
         <v>17</v>
@@ -4418,7 +4406,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B198" t="s">
         <v>8</v>
@@ -4432,7 +4420,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B199" t="s">
         <v>5</v>
@@ -4446,7 +4434,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B200" t="s">
         <v>18</v>
@@ -4460,7 +4448,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B201" t="s">
         <v>14</v>
@@ -4469,12 +4457,12 @@
         <v>14</v>
       </c>
       <c r="D201" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B202" t="s">
         <v>4</v>
@@ -4488,7 +4476,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B203" t="s">
         <v>6</v>
@@ -4502,7 +4490,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B204" t="s">
         <v>17</v>
@@ -4516,7 +4504,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B205" t="s">
         <v>8</v>
@@ -4530,7 +4518,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B206" t="s">
         <v>5</v>
@@ -4544,7 +4532,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B207" t="s">
         <v>18</v>
@@ -4558,7 +4546,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B208" t="s">
         <v>14</v>
@@ -4567,12 +4555,12 @@
         <v>14</v>
       </c>
       <c r="D208" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B209" t="s">
         <v>14</v>
@@ -4581,12 +4569,12 @@
         <v>14</v>
       </c>
       <c r="D209" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
@@ -4600,7 +4588,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B211" t="s">
         <v>6</v>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B212" t="s">
         <v>17</v>
@@ -4628,7 +4616,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B213" t="s">
         <v>8</v>
@@ -4642,7 +4630,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B214" t="s">
         <v>5</v>
@@ -4656,7 +4644,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B215" t="s">
         <v>18</v>
@@ -4670,7 +4658,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B216" t="s">
         <v>14</v>
@@ -4679,12 +4667,12 @@
         <v>14</v>
       </c>
       <c r="D216" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
@@ -4698,7 +4686,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B218" t="s">
         <v>6</v>
@@ -4712,7 +4700,7 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B219" t="s">
         <v>17</v>
@@ -4726,7 +4714,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B220" t="s">
         <v>8</v>
@@ -4740,7 +4728,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B221" t="s">
         <v>5</v>
@@ -4754,7 +4742,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B222" t="s">
         <v>18</v>
@@ -4768,7 +4756,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B223" t="s">
         <v>14</v>
@@ -4777,26 +4765,26 @@
         <v>14</v>
       </c>
       <c r="D223" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B224" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C224" t="s">
         <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B225" t="s">
         <v>14</v>
@@ -4805,54 +4793,54 @@
         <v>14</v>
       </c>
       <c r="D225" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B226" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C226" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D226" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B227" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C227" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D227" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
+        <v>203</v>
+      </c>
+      <c r="B228" t="s">
         <v>207</v>
       </c>
-      <c r="B228" t="s">
-        <v>211</v>
-      </c>
       <c r="C228" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D228" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B229" t="s">
         <v>14</v>
@@ -4861,26 +4849,26 @@
         <v>14</v>
       </c>
       <c r="D229" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B230" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C230" t="s">
         <v>14</v>
       </c>
       <c r="D230" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B231" t="s">
         <v>14</v>
@@ -4889,26 +4877,26 @@
         <v>14</v>
       </c>
       <c r="D231" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B232" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C232" t="s">
         <v>14</v>
       </c>
       <c r="D232" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B233" t="s">
         <v>14</v>
@@ -4917,40 +4905,40 @@
         <v>14</v>
       </c>
       <c r="D233" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B234" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C234" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D234" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B235" t="s">
         <v>14</v>
       </c>
       <c r="C235" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D235" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B236" t="s">
         <v>4</v>
@@ -4964,7 +4952,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B237" t="s">
         <v>6</v>
@@ -4978,7 +4966,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B238" t="s">
         <v>17</v>
@@ -4992,7 +4980,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B239" t="s">
         <v>8</v>
@@ -5006,7 +4994,7 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B240" t="s">
         <v>5</v>
@@ -5020,7 +5008,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B241" t="s">
         <v>18</v>
@@ -5034,7 +5022,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B242" t="s">
         <v>14</v>
@@ -5043,12 +5031,12 @@
         <v>14</v>
       </c>
       <c r="D242" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B243" t="s">
         <v>14</v>
@@ -5057,12 +5045,12 @@
         <v>14</v>
       </c>
       <c r="D243" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B244" t="s">
         <v>4</v>
@@ -5076,7 +5064,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B245" t="s">
         <v>6</v>
@@ -5090,7 +5078,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B246" t="s">
         <v>17</v>
@@ -5104,7 +5092,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B247" t="s">
         <v>8</v>
@@ -5118,7 +5106,7 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B248" t="s">
         <v>5</v>
@@ -5132,7 +5120,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B249" t="s">
         <v>18</v>
@@ -5146,7 +5134,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B250" t="s">
         <v>14</v>
@@ -5155,12 +5143,12 @@
         <v>14</v>
       </c>
       <c r="D250" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B251" t="s">
         <v>14</v>
@@ -5169,96 +5157,96 @@
         <v>14</v>
       </c>
       <c r="D251" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B252" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C252" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D252" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B253" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C253" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D253" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B254" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C254" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D254" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C255" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D255" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B256" t="s">
         <v>14</v>
       </c>
       <c r="C256" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D256" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B257" t="s">
         <v>14</v>
       </c>
       <c r="C257" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D257" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B258" t="s">
         <v>4</v>
@@ -5272,7 +5260,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B259" t="s">
         <v>6</v>
@@ -5286,7 +5274,7 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B260" t="s">
         <v>17</v>
@@ -5300,7 +5288,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B261" t="s">
         <v>8</v>
@@ -5314,7 +5302,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B262" t="s">
         <v>5</v>
@@ -5328,7 +5316,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B263" t="s">
         <v>18</v>
@@ -5342,7 +5330,7 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B264" t="s">
         <v>14</v>
@@ -5351,12 +5339,12 @@
         <v>14</v>
       </c>
       <c r="D264" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B265" t="s">
         <v>4</v>
@@ -5370,7 +5358,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B266" t="s">
         <v>6</v>
@@ -5384,7 +5372,7 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B267" t="s">
         <v>17</v>
@@ -5398,7 +5386,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B268" t="s">
         <v>8</v>
@@ -5412,7 +5400,7 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B269" t="s">
         <v>5</v>
@@ -5426,7 +5414,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B270" t="s">
         <v>18</v>
@@ -5440,7 +5428,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B271" t="s">
         <v>14</v>
@@ -5449,12 +5437,12 @@
         <v>14</v>
       </c>
       <c r="D271" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B272" t="s">
         <v>4</v>
@@ -5468,7 +5456,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B273" t="s">
         <v>6</v>
@@ -5482,7 +5470,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B274" t="s">
         <v>17</v>
@@ -5496,7 +5484,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B275" t="s">
         <v>8</v>
@@ -5510,7 +5498,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B276" t="s">
         <v>5</v>
@@ -5524,7 +5512,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B277" t="s">
         <v>18</v>
@@ -5538,7 +5526,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B278" t="s">
         <v>14</v>
@@ -5547,12 +5535,12 @@
         <v>14</v>
       </c>
       <c r="D278" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B279" t="s">
         <v>4</v>
@@ -5566,7 +5554,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B280" t="s">
         <v>6</v>
@@ -5580,7 +5568,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B281" t="s">
         <v>4</v>
@@ -5594,7 +5582,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B282" t="s">
         <v>6</v>
@@ -5608,7 +5596,7 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B283" t="s">
         <v>17</v>
@@ -5622,7 +5610,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B284" t="s">
         <v>8</v>
@@ -5636,7 +5624,7 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B285" t="s">
         <v>5</v>
@@ -5650,7 +5638,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B286" t="s">
         <v>18</v>
@@ -5664,7 +5652,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B287" t="s">
         <v>14</v>
@@ -5673,12 +5661,12 @@
         <v>14</v>
       </c>
       <c r="D287" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B288" t="s">
         <v>4</v>
@@ -5692,7 +5680,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B289" t="s">
         <v>6</v>
@@ -5706,10 +5694,10 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B290" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -5720,7 +5708,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B291" t="s">
         <v>8</v>
@@ -5734,7 +5722,7 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B292" t="s">
         <v>5</v>
@@ -5748,7 +5736,7 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B293" t="s">
         <v>10</v>
@@ -5762,7 +5750,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B294" t="s">
         <v>14</v>
@@ -5771,40 +5759,40 @@
         <v>14</v>
       </c>
       <c r="D294" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B295" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C295" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D295" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B296" t="s">
         <v>14</v>
       </c>
       <c r="C296" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D296" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B297" t="s">
         <v>14</v>
@@ -5813,12 +5801,12 @@
         <v>14</v>
       </c>
       <c r="D297" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B298" t="s">
         <v>4</v>
@@ -5832,7 +5820,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B299" t="s">
         <v>6</v>
@@ -5846,7 +5834,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B300" t="s">
         <v>17</v>
@@ -5860,7 +5848,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B301" t="s">
         <v>8</v>
@@ -5874,7 +5862,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B302" t="s">
         <v>5</v>
@@ -5888,7 +5876,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B303" t="s">
         <v>18</v>
@@ -5902,7 +5890,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B304" t="s">
         <v>11</v>
@@ -5916,7 +5904,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B305" t="s">
         <v>12</v>
@@ -5930,7 +5918,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B306" t="s">
         <v>13</v>
@@ -5944,7 +5932,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B307" t="s">
         <v>14</v>
@@ -5953,12 +5941,12 @@
         <v>14</v>
       </c>
       <c r="D307" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B308" t="s">
         <v>14</v>
@@ -5967,40 +5955,40 @@
         <v>14</v>
       </c>
       <c r="D308" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B309" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C309" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D309" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B310" t="s">
         <v>14</v>
       </c>
       <c r="C310" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D310" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B311" t="s">
         <v>4</v>
@@ -6014,7 +6002,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B312" t="s">
         <v>6</v>
@@ -6028,7 +6016,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B313" t="s">
         <v>17</v>
@@ -6042,7 +6030,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B314" t="s">
         <v>8</v>
@@ -6056,7 +6044,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B315" t="s">
         <v>5</v>
@@ -6070,7 +6058,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B316" t="s">
         <v>18</v>
@@ -6084,7 +6072,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B317" t="s">
         <v>11</v>
@@ -6098,7 +6086,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B318" t="s">
         <v>12</v>
@@ -6112,7 +6100,7 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B319" t="s">
         <v>13</v>
@@ -6126,7 +6114,7 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B320" t="s">
         <v>4</v>
@@ -6140,7 +6128,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B321" t="s">
         <v>6</v>
@@ -6154,7 +6142,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B322" t="s">
         <v>17</v>
@@ -6168,7 +6156,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B323" t="s">
         <v>8</v>
@@ -6182,7 +6170,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B324" t="s">
         <v>5</v>
@@ -6196,7 +6184,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B325" t="s">
         <v>18</v>
@@ -6210,7 +6198,7 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B326" t="s">
         <v>11</v>
@@ -6224,7 +6212,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B327" t="s">
         <v>12</v>
@@ -6238,7 +6226,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B328" t="s">
         <v>13</v>
@@ -6252,7 +6240,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B329" t="s">
         <v>14</v>
@@ -6261,12 +6249,12 @@
         <v>14</v>
       </c>
       <c r="D329" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B330" t="s">
         <v>4</v>
@@ -6280,7 +6268,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B331" t="s">
         <v>6</v>
@@ -6294,7 +6282,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B332" t="s">
         <v>17</v>
@@ -6308,7 +6296,7 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B333" t="s">
         <v>8</v>
@@ -6322,7 +6310,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B334" t="s">
         <v>5</v>
@@ -6336,7 +6324,7 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B335" t="s">
         <v>18</v>
@@ -6350,7 +6338,7 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B336" t="s">
         <v>14</v>
@@ -6359,54 +6347,54 @@
         <v>14</v>
       </c>
       <c r="D336" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="B337" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C337" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D337" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="B338" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C338" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D338" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="B339" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="C339" t="s">
         <v>179</v>
       </c>
       <c r="D339" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B340" t="s">
         <v>14</v>
@@ -6415,12 +6403,12 @@
         <v>14</v>
       </c>
       <c r="D340" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B341" t="s">
         <v>14</v>
@@ -6429,15 +6417,11 @@
         <v>14</v>
       </c>
       <c r="D341" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D341" xr:uid="{401FE460-E684-1845-B4A4-30BCCC5E1D62}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D341">
-      <sortCondition ref="A1:A341"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:D341" xr:uid="{401FE460-E684-1845-B4A4-30BCCC5E1D62}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>